--- a/marketing_report/outputs/Presupuesto_ROI/Presupuesto_ROI_Datos.xlsx
+++ b/marketing_report/outputs/Presupuesto_ROI/Presupuesto_ROI_Datos.xlsx
@@ -2476,25 +2476,25 @@
         <v>47387402.9</v>
       </c>
       <c r="E2">
-        <v>17829</v>
+        <v>20069</v>
       </c>
       <c r="F2">
-        <v>961</v>
+        <v>1091</v>
       </c>
       <c r="G2">
-        <v>5.39</v>
+        <v>5.44</v>
       </c>
       <c r="H2">
-        <v>2657.88</v>
+        <v>2361.22</v>
       </c>
       <c r="I2">
-        <v>49310.51</v>
+        <v>43434.83</v>
       </c>
       <c r="J2">
-        <v>170607520</v>
+        <v>196385765</v>
       </c>
       <c r="K2">
-        <v>260.03</v>
+        <v>314.43</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2511,25 +2511,25 @@
         <v>103390570.59</v>
       </c>
       <c r="E3">
-        <v>110575</v>
+        <v>122117</v>
       </c>
       <c r="F3">
-        <v>784</v>
+        <v>844</v>
       </c>
       <c r="G3">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H3">
-        <v>935.03</v>
+        <v>846.65</v>
       </c>
       <c r="I3">
-        <v>131875.73</v>
+        <v>122500.68</v>
       </c>
       <c r="J3">
-        <v>134716625</v>
+        <v>145227530</v>
       </c>
       <c r="K3">
-        <v>30.3</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2546,13 +2546,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5886</v>
+        <v>7020</v>
       </c>
       <c r="F4">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="G4">
-        <v>6.3</v>
+        <v>6.51</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>76039550</v>
+        <v>91387710</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -2581,13 +2581,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>17805</v>
+        <v>20688</v>
       </c>
       <c r="F5">
-        <v>3776</v>
+        <v>4519</v>
       </c>
       <c r="G5">
-        <v>21.21</v>
+        <v>21.84</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>669356900</v>
+        <v>804128980</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>839000</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2651,25 +2651,25 @@
         <v>1656620.95</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
-        <v>127432.38</v>
+        <v>1656620.95</v>
       </c>
       <c r="I7">
-        <v>127432.38</v>
+        <v>1656620.95</v>
       </c>
       <c r="J7">
-        <v>2057300</v>
+        <v>56500</v>
       </c>
       <c r="K7">
-        <v>24.19</v>
+        <v>-96.59</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2686,13 +2686,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>7601200</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>8857600</v>
+        <v>250000</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -2923,19 +2923,19 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>961</v>
+        <v>1091</v>
       </c>
       <c r="D2">
-        <v>170607520</v>
+        <v>196385765</v>
       </c>
       <c r="E2">
-        <v>1005</v>
+        <v>1141</v>
       </c>
       <c r="F2">
-        <v>178784915</v>
+        <v>205921300</v>
       </c>
       <c r="G2">
-        <v>-44</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2946,19 +2946,19 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>784</v>
+        <v>844</v>
       </c>
       <c r="D3">
-        <v>134716625</v>
+        <v>145227530</v>
       </c>
       <c r="E3">
-        <v>866</v>
+        <v>949</v>
       </c>
       <c r="F3">
-        <v>149947295</v>
+        <v>164481535</v>
       </c>
       <c r="G3">
-        <v>-82</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2969,19 +2969,19 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="D4">
-        <v>76039550</v>
+        <v>91387710</v>
       </c>
       <c r="E4">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F4">
-        <v>48222310</v>
+        <v>54773495</v>
       </c>
       <c r="G4">
-        <v>139</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2992,19 +2992,19 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>3776</v>
+        <v>4519</v>
       </c>
       <c r="D5">
-        <v>669356900</v>
+        <v>804128980</v>
       </c>
       <c r="E5">
-        <v>3789</v>
+        <v>4546</v>
       </c>
       <c r="F5">
-        <v>673766075</v>
+        <v>811953655</v>
       </c>
       <c r="G5">
-        <v>-13</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3015,19 +3015,19 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>839000</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1006600</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3038,19 +3038,19 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>2057300</v>
+        <v>56500</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2392900</v>
+        <v>56500</v>
       </c>
       <c r="G7">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3061,19 +3061,19 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>7601200</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>7074500</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3084,16 +3084,16 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>8857600</v>
+        <v>250000</v>
       </c>
       <c r="E9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>8881100</v>
+        <v>250000</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3113,13 +3113,13 @@
         <v>418500</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>418500</v>
+        <v>175500</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3136,13 +3136,13 @@
         <v>1227600</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>1227600</v>
+        <v>1470600</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
